--- a/outputs/11276.xlsx
+++ b/outputs/11276.xlsx
@@ -422,335 +422,335 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="5" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="5" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="9" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="13" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="13" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="12" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="14" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="14" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1145,127 +1145,127 @@
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="24" t="str">
-        <f aca="false">TEXT(F4,"ddd")</f>
+        <f aca="false">TEXT(F4,"DDD")</f>
         <v>Wed</v>
       </c>
       <c r="G3" s="25" t="str">
-        <f aca="false">TEXT(G4,"ddd")</f>
+        <f aca="false">TEXT(G4,"DDD")</f>
         <v>Thu</v>
       </c>
       <c r="H3" s="25" t="str">
-        <f aca="false">TEXT(H4,"ddd")</f>
+        <f aca="false">TEXT(H4,"DDD")</f>
         <v>Fri</v>
       </c>
       <c r="I3" s="26" t="str">
-        <f aca="false">TEXT(I4,"ddd")</f>
+        <f aca="false">TEXT(I4,"DDD")</f>
         <v>Sat</v>
       </c>
       <c r="J3" s="27" t="str">
-        <f aca="false">TEXT(J4,"ddd")</f>
+        <f aca="false">TEXT(J4,"DDD")</f>
         <v>Sun</v>
       </c>
       <c r="K3" s="25" t="str">
-        <f aca="false">TEXT(K4,"ddd")</f>
+        <f aca="false">TEXT(K4,"DDD")</f>
         <v>Mon</v>
       </c>
       <c r="L3" s="25" t="str">
-        <f aca="false">TEXT(L4,"ddd")</f>
+        <f aca="false">TEXT(L4,"DDD")</f>
         <v>Tue</v>
       </c>
       <c r="M3" s="25" t="str">
-        <f aca="false">TEXT(M4,"ddd")</f>
+        <f aca="false">TEXT(M4,"DDD")</f>
         <v>Wed</v>
       </c>
       <c r="N3" s="25" t="str">
-        <f aca="false">TEXT(N4,"ddd")</f>
+        <f aca="false">TEXT(N4,"DDD")</f>
         <v>Thu</v>
       </c>
       <c r="O3" s="25" t="str">
-        <f aca="false">TEXT(O4,"ddd")</f>
+        <f aca="false">TEXT(O4,"DDD")</f>
         <v>Fri</v>
       </c>
       <c r="P3" s="27" t="str">
-        <f aca="false">TEXT(P4,"ddd")</f>
+        <f aca="false">TEXT(P4,"DDD")</f>
         <v>Sat</v>
       </c>
       <c r="Q3" s="26" t="str">
-        <f aca="false">TEXT(Q4,"ddd")</f>
+        <f aca="false">TEXT(Q4,"DDD")</f>
         <v>Sun</v>
       </c>
       <c r="R3" s="27" t="str">
-        <f aca="false">TEXT(R4,"ddd")</f>
+        <f aca="false">TEXT(R4,"DDD")</f>
         <v>Mon</v>
       </c>
       <c r="S3" s="25" t="str">
-        <f aca="false">TEXT(S4,"ddd")</f>
+        <f aca="false">TEXT(S4,"DDD")</f>
         <v>Tue</v>
       </c>
       <c r="T3" s="25" t="str">
-        <f aca="false">TEXT(T4,"ddd")</f>
+        <f aca="false">TEXT(T4,"DDD")</f>
         <v>Wed</v>
       </c>
       <c r="U3" s="25" t="str">
-        <f aca="false">TEXT(U4,"ddd")</f>
+        <f aca="false">TEXT(U4,"DDD")</f>
         <v>Thu</v>
       </c>
       <c r="V3" s="25" t="str">
-        <f aca="false">TEXT(V4,"ddd")</f>
+        <f aca="false">TEXT(V4,"DDD")</f>
         <v>Fri</v>
       </c>
       <c r="W3" s="25" t="str">
-        <f aca="false">TEXT(W4,"ddd")</f>
+        <f aca="false">TEXT(W4,"DDD")</f>
         <v>Sat</v>
       </c>
       <c r="X3" s="26" t="str">
-        <f aca="false">TEXT(X4,"ddd")</f>
+        <f aca="false">TEXT(X4,"DDD")</f>
         <v>Sun</v>
       </c>
       <c r="Y3" s="27" t="str">
-        <f aca="false">TEXT(Y4,"ddd")</f>
+        <f aca="false">TEXT(Y4,"DDD")</f>
         <v>Mon</v>
       </c>
       <c r="Z3" s="25" t="str">
-        <f aca="false">TEXT(Z4,"ddd")</f>
+        <f aca="false">TEXT(Z4,"DDD")</f>
         <v>Tue</v>
       </c>
       <c r="AA3" s="25" t="str">
-        <f aca="false">TEXT(AA4,"ddd")</f>
+        <f aca="false">TEXT(AA4,"DDD")</f>
         <v>Wed</v>
       </c>
       <c r="AB3" s="25" t="str">
-        <f aca="false">TEXT(AB4,"ddd")</f>
+        <f aca="false">TEXT(AB4,"DDD")</f>
         <v>Thu</v>
       </c>
       <c r="AC3" s="25" t="str">
-        <f aca="false">TEXT(AC4,"ddd")</f>
+        <f aca="false">TEXT(AC4,"DDD")</f>
         <v>Fri</v>
       </c>
       <c r="AD3" s="25" t="str">
-        <f aca="false">TEXT(AD4,"ddd")</f>
+        <f aca="false">TEXT(AD4,"DDD")</f>
         <v>Sat</v>
       </c>
       <c r="AE3" s="26" t="str">
-        <f aca="false">TEXT(AE4,"ddd")</f>
+        <f aca="false">TEXT(AE4,"DDD")</f>
         <v>Sun</v>
       </c>
       <c r="AF3" s="27" t="str">
-        <f aca="false">TEXT(AF4,"ddd")</f>
+        <f aca="false">TEXT(AF4,"DDD")</f>
         <v>Mon</v>
       </c>
       <c r="AG3" s="25" t="str">
-        <f aca="false">TEXT(AG4,"ddd")</f>
+        <f aca="false">TEXT(AG4,"DDD")</f>
         <v>Tue</v>
       </c>
       <c r="AH3" s="25" t="str">
-        <f aca="false">TEXT(AH4,"ddd")</f>
+        <f aca="false">TEXT(AH4,"DDD")</f>
         <v>Wed</v>
       </c>
       <c r="AI3" s="25" t="str">
-        <f aca="false">TEXT(AI4,"ddd")</f>
+        <f aca="false">TEXT(AI4,"DDD")</f>
         <v>Thu</v>
       </c>
       <c r="AJ3" s="25" t="str">
-        <f aca="false">TEXT(AJ4,"ddd")</f>
+        <f aca="false">TEXT(AJ4,"DDD")</f>
         <v>Fri</v>
       </c>
       <c r="AK3" s="27" t="s">

--- a/outputs/11276.xlsx
+++ b/outputs/11276.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="34">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -34,13 +34,25 @@
     <t xml:space="preserve">Previous </t>
   </si>
   <si>
+    <t xml:space="preserve">TU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH</t>
+  </si>
+  <si>
     <t xml:space="preserve">F</t>
   </si>
   <si>
-    <t xml:space="preserve">W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH</t>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
   </si>
   <si>
     <t xml:space="preserve">CURRENT PENDING </t>
@@ -1145,131 +1157,101 @@
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="24" t="str">
-        <f aca="false">TEXT(F4,"DDD")</f>
+        <f aca="false">TEXT(F4,"ddd")</f>
         <v>Wed</v>
       </c>
-      <c r="G3" s="25" t="str">
-        <f aca="false">TEXT(G4,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="H3" s="25" t="str">
-        <f aca="false">TEXT(H4,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="I3" s="26" t="str">
-        <f aca="false">TEXT(I4,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="J3" s="27" t="str">
-        <f aca="false">TEXT(J4,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="K3" s="25" t="str">
-        <f aca="false">TEXT(K4,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="L3" s="25" t="str">
-        <f aca="false">TEXT(L4,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="M3" s="25" t="str">
-        <f aca="false">TEXT(M4,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="N3" s="25" t="str">
-        <f aca="false">TEXT(N4,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="O3" s="25" t="str">
-        <f aca="false">TEXT(O4,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="P3" s="27" t="str">
-        <f aca="false">TEXT(P4,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="Q3" s="26" t="str">
-        <f aca="false">TEXT(Q4,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="R3" s="27" t="str">
-        <f aca="false">TEXT(R4,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="S3" s="25" t="str">
-        <f aca="false">TEXT(S4,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="T3" s="25" t="str">
-        <f aca="false">TEXT(T4,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="U3" s="25" t="str">
-        <f aca="false">TEXT(U4,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="V3" s="25" t="str">
-        <f aca="false">TEXT(V4,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="W3" s="25" t="str">
-        <f aca="false">TEXT(W4,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="X3" s="26" t="str">
-        <f aca="false">TEXT(X4,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="Y3" s="27" t="str">
-        <f aca="false">TEXT(Y4,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="Z3" s="25" t="str">
-        <f aca="false">TEXT(Z4,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="AA3" s="25" t="str">
-        <f aca="false">TEXT(AA4,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="AB3" s="25" t="str">
-        <f aca="false">TEXT(AB4,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="AC3" s="25" t="str">
-        <f aca="false">TEXT(AC4,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="AD3" s="25" t="str">
-        <f aca="false">TEXT(AD4,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="AE3" s="26" t="str">
-        <f aca="false">TEXT(AE4,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="AF3" s="27" t="str">
-        <f aca="false">TEXT(AF4,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="AG3" s="25" t="str">
-        <f aca="false">TEXT(AG4,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="AH3" s="25" t="str">
-        <f aca="false">TEXT(AH4,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="AI3" s="25" t="str">
-        <f aca="false">TEXT(AI4,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="AJ3" s="25" t="str">
-        <f aca="false">TEXT(AJ4,"DDD")</f>
-        <v>Fri</v>
+      <c r="G3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="U3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="W3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" s="25" t="s">
+        <v>3</v>
       </c>
       <c r="AK3" s="27" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AL3" s="25" t="s">
         <v>4</v>
@@ -1278,29 +1260,29 @@
         <v>5</v>
       </c>
       <c r="AN3" s="27" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO3" s="28" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AP3" s="28"/>
       <c r="AQ3" s="28"/>
     </row>
     <row r="4" s="29" customFormat="true" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F4" s="34" t="n">
         <v>42298</v>
@@ -1408,18 +1390,18 @@
         <v>24</v>
       </c>
       <c r="AO4" s="36" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AP4" s="37" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AQ4" s="38" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" s="49" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
@@ -1470,7 +1452,7 @@
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="52" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" s="53" t="n">
         <f aca="false">18-1</f>
@@ -1498,7 +1480,7 @@
       </c>
       <c r="J6" s="54" t="str">
         <f aca="false">IF(J3="F","O","P")</f>
-        <v>P</v>
+        <v>O</v>
       </c>
       <c r="K6" s="54" t="str">
         <f aca="false">IF(K3="F","O","P")</f>
@@ -1522,14 +1504,14 @@
       </c>
       <c r="P6" s="54" t="str">
         <f aca="false">IF(P3="F","O","P")</f>
-        <v>P</v>
+        <v>O</v>
       </c>
       <c r="Q6" s="54" t="str">
         <f aca="false">IF(Q3="F","O","P")</f>
         <v>P</v>
       </c>
       <c r="R6" s="54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S6" s="54" t="str">
         <f aca="false">IF(S3="F","O","P")</f>
@@ -1556,7 +1538,7 @@
         <v>P</v>
       </c>
       <c r="Y6" s="54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Z6" s="54" t="str">
         <f aca="false">IF(Z3="F","O","P")</f>
@@ -1579,10 +1561,10 @@
         <v>P</v>
       </c>
       <c r="AE6" s="54" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AF6" s="54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AG6" s="54" t="str">
         <f aca="false">IF(AG3="F","O","P")</f>
@@ -1601,7 +1583,7 @@
         <v>P</v>
       </c>
       <c r="AK6" s="54" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AL6" s="50"/>
       <c r="AM6" s="55"/>
@@ -1624,10 +1606,10 @@
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="60"/>
       <c r="F8" s="61" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G8" s="62" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -1635,10 +1617,10 @@
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D9" s="1"/>
       <c r="F9" s="50" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -1668,10 +1650,10 @@
       <c r="D10" s="1"/>
       <c r="E10" s="69"/>
       <c r="F10" s="70" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
@@ -1696,10 +1678,10 @@
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F11" s="70" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G11" s="76" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -1721,10 +1703,10 @@
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="60"/>
       <c r="F12" s="78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G12" s="79" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1734,26 +1716,26 @@
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F13" s="81" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F14" s="82" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F15" s="82" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
